--- a/maps/globe-edaw.xlsx
+++ b/maps/globe-edaw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathan/Projects/moraldespair/maps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A148B1C3-56A5-924A-866C-780A79A16E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40498C1-3DA3-5B48-BF4C-8AD3A0D24182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="19480" xr2:uid="{3B5E9257-A34F-FB4C-A358-5A3CFDE8EC88}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Globe" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Globe!$A$2:$AX$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Globe!$A$1:$AX$51</definedName>
   </definedNames>
   <calcPr calcId="92512"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2502" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2501" uniqueCount="49">
   <si>
     <t>M</t>
   </si>
@@ -82,9 +82,6 @@
     <t>j</t>
   </si>
   <si>
-    <t>Moral Decay</t>
-  </si>
-  <si>
     <t>nv</t>
   </si>
   <si>
@@ -133,9 +130,6 @@
     <t>forest</t>
   </si>
   <si>
-    <t>Pylus</t>
-  </si>
-  <si>
     <t>foothills</t>
   </si>
   <si>
@@ -182,7 +176,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -191,11 +185,6 @@
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="72"/>
-      <name val="Umbra"/>
       <family val="2"/>
     </font>
     <font>
@@ -359,7 +348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -449,9 +438,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -771,68 +757,318 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:AY131"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" thickTop="1" thickBottom="1"/>
+  <dimension ref="A1:AY131"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" thickTop="1" thickBottom="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="49" width="8.83203125" customWidth="1"/>
     <col min="50" max="50" width="9.1640625" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:50" ht="80" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A2" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-      <c r="AE2" s="30"/>
-      <c r="AF2" s="30"/>
-      <c r="AG2" s="30"/>
-      <c r="AH2" s="30"/>
-      <c r="AI2" s="30"/>
-      <c r="AJ2" s="30"/>
-      <c r="AK2" s="30"/>
-      <c r="AL2" s="30"/>
-      <c r="AM2" s="30"/>
-      <c r="AN2" s="30"/>
-      <c r="AO2" s="30"/>
-      <c r="AP2" s="30"/>
-      <c r="AQ2" s="30"/>
-      <c r="AR2" s="30"/>
-      <c r="AS2" s="30"/>
-      <c r="AT2" s="30"/>
-      <c r="AU2" s="30"/>
-      <c r="AV2" s="30"/>
-      <c r="AW2" s="30"/>
-      <c r="AX2" s="30"/>
-    </row>
-    <row r="3" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="1" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AU1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AV1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AW1" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AW2" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX2" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -899,23 +1135,23 @@
       <c r="V3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="W3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB3" s="1" t="s">
-        <v>2</v>
+      <c r="W3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="X3" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="AC3" s="2" t="s">
         <v>6</v>
@@ -932,14 +1168,14 @@
       <c r="AG3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AH3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="5" t="s">
-        <v>11</v>
+      <c r="AH3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="AK3" s="1" t="s">
         <v>2</v>
@@ -962,29 +1198,29 @@
       <c r="AQ3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AR3" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS3" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AT3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AU3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AW3" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+      <c r="AR3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW3" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1048,26 +1284,26 @@
       <c r="U4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="V4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>2</v>
+      <c r="V4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="AC4" s="2" t="s">
         <v>6</v>
@@ -1090,11 +1326,11 @@
       <c r="AI4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AJ4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK4" s="1" t="s">
-        <v>2</v>
+      <c r="AJ4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK4" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AL4" s="1" t="s">
         <v>2</v>
@@ -1114,29 +1350,29 @@
       <c r="AQ4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AR4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AT4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AU4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AV4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AW4" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="AX4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+      <c r="AR4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW4" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -1200,175 +1436,175 @@
       <c r="U5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="V5" s="1" t="s">
-        <v>2</v>
+      <c r="V5" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="W5" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="X5" s="16" t="s">
+      <c r="X5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AV5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW5" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX5" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="V6" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="W6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Y5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AJ5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AK5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AU5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AV5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AW5" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="AX5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V6" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="W6" s="9" t="s">
-        <v>3</v>
-      </c>
       <c r="X6" s="9" t="s">
         <v>3</v>
       </c>
       <c r="Y6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="Z6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>6</v>
+      <c r="Z6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA6" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AB6" s="2" t="s">
         <v>6</v>
@@ -1379,20 +1615,20 @@
       <c r="AD6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AE6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AI6" s="2" t="s">
-        <v>6</v>
+      <c r="AE6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI6" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AJ6" s="9" t="s">
         <v>3</v>
@@ -1400,35 +1636,35 @@
       <c r="AK6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AL6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AU6" s="5" t="s">
-        <v>11</v>
+      <c r="AL6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AQ6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AS6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AU6" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AV6" s="1" t="s">
         <v>2</v>
@@ -1440,7 +1676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="7" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -1456,26 +1692,26 @@
       <c r="E7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>2</v>
+      <c r="F7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>2</v>
+      <c r="I7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>2</v>
@@ -1505,7 +1741,7 @@
         <v>2</v>
       </c>
       <c r="V7" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>3</v>
@@ -1516,29 +1752,29 @@
       <c r="Y7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="Z7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA7" s="4" t="s">
-        <v>46</v>
+      <c r="Z7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>6</v>
+      <c r="AC7" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AD7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG7" s="2" t="s">
-        <v>6</v>
+      <c r="AE7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG7" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AH7" s="9" t="s">
         <v>3</v>
@@ -1546,8 +1782,8 @@
       <c r="AI7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AJ7" s="9" t="s">
-        <v>3</v>
+      <c r="AJ7" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AK7" s="9" t="s">
         <v>3</v>
@@ -1558,26 +1794,26 @@
       <c r="AM7" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AN7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT7" s="5" t="s">
-        <v>11</v>
+      <c r="AN7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AQ7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AR7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AS7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AT7" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AU7" s="5" t="s">
         <v>11</v>
@@ -1592,18 +1828,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="8" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>2</v>
+      <c r="C8" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>2</v>
@@ -1611,11 +1847,11 @@
       <c r="F8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>6</v>
+      <c r="G8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>13</v>
@@ -1626,14 +1862,14 @@
       <c r="K8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>2</v>
+      <c r="L8" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>2</v>
@@ -1653,17 +1889,17 @@
       <c r="T8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U8" s="4" t="s">
-        <v>44</v>
+      <c r="U8" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="V8" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="W8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="X8" s="9" t="s">
-        <v>3</v>
+        <v>23</v>
+      </c>
+      <c r="W8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="Y8" s="6" t="s">
         <v>5</v>
@@ -1671,32 +1907,32 @@
       <c r="Z8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AA8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>6</v>
+      <c r="AA8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD8" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AE8" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AF8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI8" s="9" t="s">
-        <v>3</v>
+      <c r="AF8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI8" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AJ8" s="9" t="s">
         <v>3</v>
@@ -1728,11 +1964,11 @@
       <c r="AS8" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AT8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AU8" s="9" t="s">
-        <v>3</v>
+      <c r="AT8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU8" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AV8" s="1" t="s">
         <v>2</v>
@@ -1744,15 +1980,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="9" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>2</v>
+      <c r="C9" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>2</v>
@@ -1760,14 +1996,14 @@
       <c r="E9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>2</v>
+      <c r="F9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="I9" s="13" t="s">
         <v>13</v>
@@ -1781,23 +2017,23 @@
       <c r="L9" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>2</v>
+      <c r="M9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="P9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="R9" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>2</v>
@@ -1809,13 +2045,13 @@
         <v>2</v>
       </c>
       <c r="V9" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="X9" s="9" t="s">
-        <v>3</v>
+      <c r="X9" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="Y9" s="6" t="s">
         <v>5</v>
@@ -1823,65 +2059,65 @@
       <c r="Z9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AA9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB9" s="2" t="s">
-        <v>6</v>
+      <c r="AA9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AC9" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AD9" s="2" t="s">
-        <v>6</v>
+      <c r="AD9" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AE9" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AF9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ9" s="5" t="s">
-        <v>11</v>
+      <c r="AF9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ9" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AK9" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AL9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AM9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AN9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO9" s="9" t="s">
-        <v>3</v>
+      <c r="AL9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO9" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="AP9" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AQ9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AR9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AS9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AT9" s="9" t="s">
-        <v>3</v>
+      <c r="AQ9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AR9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AS9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT9" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AU9" s="5" t="s">
         <v>11</v>
@@ -1896,12 +2132,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="10" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>2</v>
+      <c r="B10" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>9</v>
@@ -1915,8 +2151,8 @@
       <c r="F10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>2</v>
+      <c r="G10" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>13</v>
@@ -1936,8 +2172,8 @@
       <c r="M10" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N10" s="13" t="s">
-        <v>13</v>
+      <c r="N10" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>2</v>
@@ -1957,17 +2193,17 @@
       <c r="T10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V10" s="17" t="s">
-        <v>24</v>
+      <c r="U10" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="V10" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="X10" s="1" t="s">
-        <v>2</v>
+      <c r="X10" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="Y10" s="6" t="s">
         <v>5</v>
@@ -1975,8 +2211,8 @@
       <c r="Z10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AA10" s="1" t="s">
-        <v>2</v>
+      <c r="AA10" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="AB10" s="9" t="s">
         <v>3</v>
@@ -1984,11 +2220,11 @@
       <c r="AC10" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AD10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE10" s="9" t="s">
-        <v>3</v>
+      <c r="AD10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AF10" s="1" t="s">
         <v>2</v>
@@ -2002,38 +2238,38 @@
       <c r="AI10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AJ10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AM10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AN10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AQ10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AR10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AS10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AT10" s="5" t="s">
-        <v>11</v>
+      <c r="AJ10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AP10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT10" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="AU10" s="5" t="s">
         <v>11</v>
@@ -2048,18 +2284,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="11" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>2</v>
+      <c r="B11" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>2</v>
+      <c r="D11" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>2</v>
@@ -2106,20 +2342,20 @@
       <c r="S11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="T11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V11" s="17" t="s">
-        <v>24</v>
+      <c r="T11" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="U11" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="V11" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="X11" s="1" t="s">
-        <v>2</v>
+      <c r="X11" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="Y11" s="6" t="s">
         <v>5</v>
@@ -2127,20 +2363,20 @@
       <c r="Z11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AA11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE11" s="9" t="s">
-        <v>3</v>
+      <c r="AA11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE11" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AF11" s="1" t="s">
         <v>2</v>
@@ -2154,11 +2390,11 @@
       <c r="AI11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AJ11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK11" s="9" t="s">
-        <v>3</v>
+      <c r="AJ11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK11" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AL11" s="13" t="s">
         <v>13</v>
@@ -2166,41 +2402,41 @@
       <c r="AM11" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="AN11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AO11" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AP11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AQ11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AR11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AS11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AT11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AU11" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AV11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AW11" s="23" t="s">
-        <v>2</v>
+      <c r="AN11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AO11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AP11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AV11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AW11" s="24" t="s">
+        <v>11</v>
       </c>
       <c r="AX11" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="12" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>2</v>
       </c>
@@ -2210,8 +2446,8 @@
       <c r="C12" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>9</v>
+      <c r="D12" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>2</v>
@@ -2219,8 +2455,8 @@
       <c r="F12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G12" s="13" t="s">
-        <v>13</v>
+      <c r="G12" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>13</v>
@@ -2258,11 +2494,11 @@
       <c r="S12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="T12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U12" s="17" t="s">
-        <v>24</v>
+      <c r="T12" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="U12" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="V12" s="9" t="s">
         <v>3</v>
@@ -2279,14 +2515,14 @@
       <c r="Z12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AA12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC12" s="9" t="s">
-        <v>3</v>
+      <c r="AA12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AD12" s="1" t="s">
         <v>2</v>
@@ -2309,20 +2545,20 @@
       <c r="AJ12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AM12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AN12" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AO12" s="5" t="s">
-        <v>11</v>
+      <c r="AK12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AN12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO12" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AP12" s="10" t="s">
         <v>12</v>
@@ -2336,34 +2572,34 @@
       <c r="AS12" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AT12" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AU12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AV12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AW12" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="AX12" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+      <c r="AT12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AU12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AV12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AW12" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="AX12" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>9</v>
+      <c r="B13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>2</v>
@@ -2371,11 +2607,11 @@
       <c r="F13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>13</v>
+      <c r="G13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>13</v>
@@ -2386,32 +2622,32 @@
       <c r="K13" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="L13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="N13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="R13" s="13" t="s">
-        <v>13</v>
+      <c r="L13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>2</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U13" s="9" t="s">
         <v>3</v>
@@ -2461,38 +2697,38 @@
       <c r="AJ13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK13" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AM13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="AN13" s="5" t="s">
-        <v>11</v>
+      <c r="AK13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN13" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AO13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AP13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AQ13" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AR13" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AS13" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="AU13" s="10" t="s">
-        <v>12</v>
+      <c r="AP13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AQ13" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AR13" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AS13" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT13" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AU13" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AV13" s="5" t="s">
         <v>11</v>
@@ -2500,19 +2736,19 @@
       <c r="AW13" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="AX13" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+      <c r="AX13" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>9</v>
+      <c r="B14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>2</v>
@@ -2526,23 +2762,23 @@
       <c r="G14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="L14" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>13</v>
+      <c r="H14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="N14" s="1" t="s">
         <v>2</v>
@@ -2563,7 +2799,7 @@
         <v>2</v>
       </c>
       <c r="T14" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U14" s="9" t="s">
         <v>3</v>
@@ -2574,8 +2810,8 @@
       <c r="W14" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="9" t="s">
-        <v>3</v>
+      <c r="X14" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="Y14" s="6" t="s">
         <v>5</v>
@@ -2610,53 +2846,53 @@
       <c r="AI14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AJ14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AM14" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AN14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AO14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AP14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AQ14" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AR14" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AS14" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AU14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AV14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AW14" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="AX14" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+      <c r="AJ14" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR14" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AS14" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT14" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU14" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW14" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX14" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>2</v>
       </c>
@@ -2681,14 +2917,14 @@
       <c r="H15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>13</v>
+      <c r="I15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="L15" s="1" t="s">
         <v>2</v>
@@ -2708,14 +2944,14 @@
       <c r="Q15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="R15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T15" s="17" t="s">
-        <v>24</v>
+      <c r="R15" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="S15" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="9" t="s">
         <v>3</v>
@@ -2762,8 +2998,8 @@
       <c r="AI15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AJ15" s="5" t="s">
-        <v>11</v>
+      <c r="AJ15" s="9" t="s">
+        <v>0</v>
       </c>
       <c r="AK15" s="1" t="s">
         <v>2</v>
@@ -2774,41 +3010,41 @@
       <c r="AM15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AN15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AO15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AP15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AQ15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AR15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AS15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AT15" s="10" t="s">
-        <v>12</v>
+      <c r="AN15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AQ15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT15" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AU15" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AV15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AW15" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="AX15" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+      <c r="AV15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW15" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX15" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>2</v>
       </c>
@@ -2827,8 +3063,8 @@
       <c r="F16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>2</v>
+      <c r="G16" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>2</v>
@@ -2854,20 +3090,20 @@
       <c r="O16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="P16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>24</v>
+      <c r="P16" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="R16" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="U16" s="9" t="s">
         <v>3</v>
@@ -2875,8 +3111,8 @@
       <c r="V16" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="W16" s="9" t="s">
-        <v>3</v>
+      <c r="W16" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="X16" s="1" t="s">
         <v>2</v>
@@ -2914,12 +3150,12 @@
       <c r="AI16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AJ16" s="9" t="s">
+      <c r="AJ16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK16" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="AK16" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="AL16" s="1" t="s">
         <v>2</v>
       </c>
@@ -2938,17 +3174,17 @@
       <c r="AQ16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AR16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AS16" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AT16" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AU16" s="12" t="s">
-        <v>9</v>
+      <c r="AR16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU16" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AV16" s="1" t="s">
         <v>2</v>
@@ -2960,30 +3196,30 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="17" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>2</v>
+      <c r="C17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>2</v>
@@ -3003,20 +3239,20 @@
       <c r="N17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R17" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="S17" s="17" t="s">
-        <v>24</v>
+      <c r="O17" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="T17" s="9" t="s">
         <v>3</v>
@@ -3027,11 +3263,11 @@
       <c r="V17" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="W17" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="X17" s="9" t="s">
-        <v>3</v>
+      <c r="W17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="Y17" s="6" t="s">
         <v>5</v>
@@ -3066,8 +3302,8 @@
       <c r="AI17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AJ17" s="9" t="s">
-        <v>0</v>
+      <c r="AJ17" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AK17" s="1" t="s">
         <v>2</v>
@@ -3112,7 +3348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="18" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>2</v>
       </c>
@@ -3125,17 +3361,17 @@
       <c r="D18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>2</v>
+      <c r="E18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>2</v>
@@ -3155,29 +3391,29 @@
       <c r="N18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P18" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q18" s="17" t="s">
-        <v>24</v>
+      <c r="O18" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="R18" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="S18" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="9" t="s">
-        <v>3</v>
+      <c r="S18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>2</v>
@@ -3218,11 +3454,11 @@
       <c r="AI18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AJ18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK18" s="9" t="s">
-        <v>0</v>
+      <c r="AJ18" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK18" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AL18" s="1" t="s">
         <v>2</v>
@@ -3264,18 +3500,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="19" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>11</v>
+      <c r="C19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>12</v>
@@ -3286,8 +3522,8 @@
       <c r="G19" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>11</v>
+      <c r="H19" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>2</v>
@@ -3307,29 +3543,29 @@
       <c r="N19" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O19" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="P19" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q19" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="R19" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="S19" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="T19" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="U19" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="V19" s="9" t="s">
-        <v>3</v>
+      <c r="O19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>2</v>
@@ -3364,26 +3600,26 @@
       <c r="AG19" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AH19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN19" s="1" t="s">
-        <v>2</v>
+      <c r="AH19" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI19" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ19" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK19" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL19" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM19" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN19" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AO19" s="1" t="s">
         <v>2</v>
@@ -3416,7 +3652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="20" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>2</v>
       </c>
@@ -3429,14 +3665,14 @@
       <c r="D20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>12</v>
+      <c r="E20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>11</v>
@@ -3444,32 +3680,32 @@
       <c r="I20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O20" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="9" t="s">
-        <v>3</v>
+      <c r="J20" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>2</v>
@@ -3513,26 +3749,26 @@
       <c r="AF20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AG20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI20" s="1" t="s">
-        <v>2</v>
+      <c r="AG20" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH20" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI20" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AJ20" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AK20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM20" s="1" t="s">
-        <v>2</v>
+      <c r="AK20" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL20" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM20" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AN20" s="1" t="s">
         <v>2</v>
@@ -3568,7 +3804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="21" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>2</v>
       </c>
@@ -3578,44 +3814,44 @@
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>2</v>
+      <c r="D21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="Q21" s="1" t="s">
         <v>2</v>
@@ -3665,8 +3901,8 @@
       <c r="AF21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AG21" s="1" t="s">
-        <v>2</v>
+      <c r="AG21" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AH21" s="12" t="s">
         <v>9</v>
@@ -3674,20 +3910,20 @@
       <c r="AI21" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AJ21" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK21" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AL21" s="12" t="s">
-        <v>9</v>
+      <c r="AJ21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL21" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AM21" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AN21" s="12" t="s">
-        <v>9</v>
+      <c r="AN21" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AO21" s="1" t="s">
         <v>2</v>
@@ -3720,12 +3956,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>2</v>
+    <row r="22" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>2</v>
@@ -3739,38 +3975,38 @@
       <c r="F22" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>2</v>
+      <c r="G22" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="9" t="s">
-        <v>3</v>
+      <c r="K22" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="L22" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="N22" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>2</v>
+      <c r="O22" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>2</v>
@@ -3805,17 +4041,17 @@
       <c r="AB22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AC22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF22" s="1" t="s">
-        <v>2</v>
+      <c r="AC22" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD22" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE22" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF22" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AG22" s="12" t="s">
         <v>9</v>
@@ -3826,23 +4062,23 @@
       <c r="AI22" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AJ22" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK22" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AL22" s="12" t="s">
-        <v>9</v>
+      <c r="AJ22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK22" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL22" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AM22" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AN22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO22" s="1" t="s">
-        <v>2</v>
+      <c r="AN22" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO22" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AP22" s="1" t="s">
         <v>2</v>
@@ -3865,16 +4101,16 @@
       <c r="AV22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AW22" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="AX22" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A23" s="1" t="s">
-        <v>2</v>
+      <c r="AW22" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX22" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>2</v>
@@ -3885,44 +4121,44 @@
       <c r="D23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="L23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K23" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>2</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>2</v>
@@ -3957,8 +4193,8 @@
       <c r="AB23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AC23" s="1" t="s">
-        <v>2</v>
+      <c r="AC23" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="AD23" s="1" t="s">
         <v>2</v>
@@ -3969,11 +4205,11 @@
       <c r="AF23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AG23" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH23" s="12" t="s">
-        <v>9</v>
+      <c r="AG23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH23" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AI23" s="12" t="s">
         <v>9</v>
@@ -3981,11 +4217,11 @@
       <c r="AJ23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK23" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL23" s="5" t="s">
-        <v>11</v>
+      <c r="AK23" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL23" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AM23" s="12" t="s">
         <v>9</v>
@@ -3993,8 +4229,8 @@
       <c r="AN23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AO23" s="1" t="s">
-        <v>2</v>
+      <c r="AO23" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AP23" s="1" t="s">
         <v>2</v>
@@ -4017,19 +4253,19 @@
       <c r="AV23" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AW23" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="AX23" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A24" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>9</v>
+      <c r="AW23" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="AX23" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>2</v>
@@ -4037,11 +4273,11 @@
       <c r="D24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>9</v>
+      <c r="E24" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>3</v>
@@ -4052,8 +4288,8 @@
       <c r="I24" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J24" s="9" t="s">
-        <v>3</v>
+      <c r="J24" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="K24" s="13" t="s">
         <v>13</v>
@@ -4076,8 +4312,8 @@
       <c r="Q24" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="1" t="s">
-        <v>2</v>
+      <c r="R24" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>2</v>
@@ -4094,8 +4330,8 @@
       <c r="W24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="X24" s="1" t="s">
-        <v>2</v>
+      <c r="X24" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="Y24" s="6" t="s">
         <v>5</v>
@@ -4106,23 +4342,23 @@
       <c r="AA24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AB24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC24" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD24" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE24" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF24" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG24" s="12" t="s">
-        <v>9</v>
+      <c r="AB24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG24" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AH24" s="12" t="s">
         <v>9</v>
@@ -4133,20 +4369,20 @@
       <c r="AJ24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK24" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL24" s="5" t="s">
-        <v>11</v>
+      <c r="AK24" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL24" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AM24" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AN24" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AO24" s="12" t="s">
-        <v>9</v>
+      <c r="AN24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO24" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AP24" s="1" t="s">
         <v>2</v>
@@ -4154,8 +4390,8 @@
       <c r="AQ24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AR24" s="1" t="s">
-        <v>2</v>
+      <c r="AR24" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="AS24" s="1" t="s">
         <v>2</v>
@@ -4166,28 +4402,28 @@
       <c r="AU24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AV24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AW24" s="25" t="s">
+      <c r="AV24" s="15" t="s">
         <v>7</v>
+      </c>
+      <c r="AW24" s="26" t="s">
+        <v>18</v>
       </c>
       <c r="AX24" s="18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A25" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>2</v>
+    <row r="25" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>13</v>
@@ -4204,8 +4440,8 @@
       <c r="I25" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J25" s="9" t="s">
-        <v>3</v>
+      <c r="J25" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="K25" s="13" t="s">
         <v>13</v>
@@ -4216,8 +4452,8 @@
       <c r="M25" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N25" s="9" t="s">
-        <v>3</v>
+      <c r="N25" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>3</v>
@@ -4225,8 +4461,8 @@
       <c r="P25" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="Q25" s="4" t="s">
-        <v>45</v>
+      <c r="Q25" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>2</v>
@@ -4243,8 +4479,8 @@
       <c r="V25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="W25" s="1" t="s">
-        <v>2</v>
+      <c r="W25" s="16" t="s">
+        <v>22</v>
       </c>
       <c r="X25" s="1" t="s">
         <v>2</v>
@@ -4258,14 +4494,14 @@
       <c r="AA25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AB25" s="1" t="s">
-        <v>2</v>
+      <c r="AB25" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="AC25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AD25" s="1" t="s">
-        <v>2</v>
+      <c r="AD25" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="AE25" s="1" t="s">
         <v>2</v>
@@ -4273,32 +4509,32 @@
       <c r="AF25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AG25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH25" s="1" t="s">
-        <v>2</v>
+      <c r="AG25" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH25" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AI25" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AJ25" s="5" t="s">
-        <v>11</v>
+      <c r="AJ25" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AK25" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AL25" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM25" s="12" t="s">
-        <v>9</v>
+      <c r="AL25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM25" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AN25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AO25" s="12" t="s">
-        <v>9</v>
+      <c r="AO25" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AP25" s="1" t="s">
         <v>2</v>
@@ -4315,11 +4551,11 @@
       <c r="AT25" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AU25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AV25" s="1" t="s">
-        <v>2</v>
+      <c r="AU25" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="AV25" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="AW25" s="25" t="s">
         <v>7</v>
@@ -4327,19 +4563,20 @@
       <c r="AX25" s="18" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="26" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
+      <c r="AY25" s="21"/>
+    </row>
+    <row r="26" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>2</v>
+      <c r="D26" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>13</v>
@@ -4368,8 +4605,8 @@
       <c r="M26" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N26" s="9" t="s">
-        <v>3</v>
+      <c r="N26" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="O26" s="9" t="s">
         <v>3</v>
@@ -4380,8 +4617,8 @@
       <c r="Q26" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="R26" s="9" t="s">
-        <v>3</v>
+      <c r="R26" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>2</v>
@@ -4395,11 +4632,11 @@
       <c r="V26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="W26" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X26" s="16" t="s">
-        <v>20</v>
+      <c r="W26" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="Y26" s="6" t="s">
         <v>5</v>
@@ -4410,8 +4647,8 @@
       <c r="AA26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AB26" s="2" t="s">
-        <v>6</v>
+      <c r="AB26" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="AC26" s="2" t="s">
         <v>6</v>
@@ -4425,8 +4662,8 @@
       <c r="AF26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AG26" s="1" t="s">
-        <v>2</v>
+      <c r="AG26" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AH26" s="12" t="s">
         <v>9</v>
@@ -4434,17 +4671,17 @@
       <c r="AI26" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AJ26" s="5" t="s">
-        <v>11</v>
+      <c r="AJ26" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AK26" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AL26" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM26" s="12" t="s">
-        <v>9</v>
+      <c r="AL26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AM26" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AN26" s="1" t="s">
         <v>2</v>
@@ -4458,8 +4695,8 @@
       <c r="AQ26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AR26" s="4" t="s">
-        <v>15</v>
+      <c r="AR26" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AS26" s="1" t="s">
         <v>2</v>
@@ -4470,25 +4707,25 @@
       <c r="AU26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AV26" s="15" t="s">
-        <v>7</v>
+      <c r="AV26" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="AW26" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="AX26" s="18" t="s">
+      <c r="AX26" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="18" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>29</v>
+      <c r="B27" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>13</v>
@@ -4496,17 +4733,17 @@
       <c r="E27" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>3</v>
+      <c r="F27" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>13</v>
@@ -4526,8 +4763,8 @@
       <c r="O27" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="9" t="s">
-        <v>3</v>
+      <c r="P27" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="Q27" s="9" t="s">
         <v>3</v>
@@ -4547,8 +4784,8 @@
       <c r="V27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="W27" s="16" t="s">
-        <v>23</v>
+      <c r="W27" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="X27" s="1" t="s">
         <v>2</v>
@@ -4556,14 +4793,14 @@
       <c r="Y27" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="Z27" s="1" t="s">
+      <c r="Z27" s="19" t="s">
         <v>2</v>
       </c>
       <c r="AA27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AB27" s="4" t="s">
-        <v>50</v>
+      <c r="AB27" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="AC27" s="2" t="s">
         <v>6</v>
@@ -4577,8 +4814,8 @@
       <c r="AF27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AG27" s="12" t="s">
-        <v>9</v>
+      <c r="AG27" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AH27" s="12" t="s">
         <v>9</v>
@@ -4619,38 +4856,37 @@
       <c r="AT27" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AU27" s="15" t="s">
-        <v>7</v>
+      <c r="AU27" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AV27" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="AW27" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="AX27" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AY27" s="21"/>
-    </row>
-    <row r="28" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
+      <c r="AW27" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="AX27" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="18" t="s">
+      <c r="B28" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>13</v>
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>3</v>
@@ -4658,14 +4894,14 @@
       <c r="H28" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="I28" s="9" t="s">
-        <v>3</v>
+      <c r="I28" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="J28" s="13" t="s">
         <v>13</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>5</v>
@@ -4775,34 +5011,34 @@
       <c r="AU28" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AV28" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AW28" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="AX28" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A29" s="18" t="s">
+      <c r="AV28" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="AW28" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>3</v>
+      <c r="AX28" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>3</v>
@@ -4810,8 +5046,8 @@
       <c r="H29" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>13</v>
+      <c r="I29" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>13</v>
@@ -4825,14 +5061,14 @@
       <c r="M29" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N29" s="13" t="s">
-        <v>13</v>
+      <c r="N29" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="1" t="s">
-        <v>2</v>
+      <c r="P29" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="Q29" s="9" t="s">
         <v>3</v>
@@ -4859,31 +5095,31 @@
         <v>2</v>
       </c>
       <c r="Y29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z29" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z29" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AA29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AB29" s="2" t="s">
-        <v>6</v>
+      <c r="AB29" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AC29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AD29" s="2" t="s">
-        <v>6</v>
+      <c r="AD29" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AE29" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AF29" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG29" s="1" t="s">
-        <v>2</v>
+      <c r="AF29" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG29" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AH29" s="12" t="s">
         <v>9</v>
@@ -4894,8 +5130,8 @@
       <c r="AJ29" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AK29" s="12" t="s">
-        <v>9</v>
+      <c r="AK29" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AL29" s="1" t="s">
         <v>2</v>
@@ -4927,23 +5163,23 @@
       <c r="AU29" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AV29" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="AW29" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="AX29" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A30" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" s="18" t="s">
+      <c r="AV29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW29" s="25" t="s">
         <v>7</v>
       </c>
+      <c r="AX29" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="C30" s="1" t="s">
         <v>2</v>
       </c>
@@ -4974,14 +5210,14 @@
       <c r="L30" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="N30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="O30" s="13" t="s">
-        <v>13</v>
+      <c r="M30" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>2</v>
@@ -5025,8 +5261,8 @@
       <c r="AC30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AD30" s="2" t="s">
-        <v>6</v>
+      <c r="AD30" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AE30" s="1" t="s">
         <v>2</v>
@@ -5040,14 +5276,14 @@
       <c r="AH30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AI30" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ30" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK30" s="12" t="s">
-        <v>9</v>
+      <c r="AI30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK30" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AL30" s="1" t="s">
         <v>2</v>
@@ -5061,14 +5297,14 @@
       <c r="AO30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AP30" s="14" t="s">
-        <v>36</v>
+      <c r="AP30" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AQ30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AR30" s="1" t="s">
-        <v>2</v>
+      <c r="AR30" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="AS30" s="1" t="s">
         <v>2</v>
@@ -5079,17 +5315,17 @@
       <c r="AU30" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AV30" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="AW30" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="AX30" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
+      <c r="AV30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW30" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX30" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>2</v>
       </c>
@@ -5099,47 +5335,47 @@
       <c r="C31" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>2</v>
+      <c r="D31" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="H31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="M31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="O31" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="P31" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q31" s="9" t="s">
-        <v>3</v>
+      <c r="H31" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="M31" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>2</v>
@@ -5177,26 +5413,26 @@
       <c r="AC31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AD31" s="1" t="s">
-        <v>2</v>
+      <c r="AD31" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="AE31" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AF31" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AG31" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH31" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI31" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AJ31" s="12" t="s">
-        <v>9</v>
+      <c r="AF31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ31" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AK31" s="1" t="s">
         <v>2</v>
@@ -5234,28 +5470,28 @@
       <c r="AV31" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AW31" s="25" t="s">
-        <v>7</v>
+      <c r="AW31" s="23" t="s">
+        <v>2</v>
       </c>
       <c r="AX31" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="32" spans="1:51" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>2</v>
+      <c r="C32" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>3</v>
@@ -5263,26 +5499,26 @@
       <c r="G32" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J32" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K32" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="L32" s="13" t="s">
-        <v>13</v>
+      <c r="H32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="L32" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="M32" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="N32" s="1" t="s">
-        <v>2</v>
+      <c r="N32" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>2</v>
@@ -5299,17 +5535,17 @@
       <c r="S32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="T32" s="1" t="s">
-        <v>2</v>
+      <c r="T32" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="U32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="V32" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W32" s="1" t="s">
-        <v>2</v>
+      <c r="V32" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="W32" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="X32" s="1" t="s">
         <v>2</v>
@@ -5347,23 +5583,23 @@
       <c r="AI32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AJ32" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK32" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL32" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM32" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN32" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO32" s="1" t="s">
-        <v>2</v>
+      <c r="AJ32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO32" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AP32" s="1" t="s">
         <v>2</v>
@@ -5371,8 +5607,8 @@
       <c r="AQ32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AR32" s="4" t="s">
-        <v>37</v>
+      <c r="AR32" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AS32" s="1" t="s">
         <v>2</v>
@@ -5393,15 +5629,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="33" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>2</v>
+      <c r="C33" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>3</v>
@@ -5415,17 +5651,17 @@
       <c r="G33" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="H33" s="9" t="s">
-        <v>3</v>
+      <c r="H33" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>2</v>
+      <c r="J33" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="L33" s="12" t="s">
         <v>9</v>
@@ -5436,8 +5672,8 @@
       <c r="N33" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="O33" s="1" t="s">
-        <v>2</v>
+      <c r="O33" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="P33" s="1" t="s">
         <v>2</v>
@@ -5448,17 +5684,17 @@
       <c r="R33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="S33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>2</v>
+      <c r="S33" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="T33" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="U33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="V33" s="1" t="s">
-        <v>2</v>
+      <c r="V33" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>2</v>
@@ -5478,11 +5714,11 @@
       <c r="AB33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AC33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD33" s="4" t="s">
-        <v>34</v>
+      <c r="AC33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD33" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AE33" s="1" t="s">
         <v>2</v>
@@ -5493,26 +5729,26 @@
       <c r="AG33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AH33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AM33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AN33" s="1" t="s">
-        <v>2</v>
+      <c r="AH33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN33" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AO33" s="1" t="s">
         <v>2</v>
@@ -5545,12 +5781,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="34" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>2</v>
+      <c r="B34" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>3</v>
@@ -5561,11 +5797,11 @@
       <c r="E34" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F34" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G34" s="9" t="s">
-        <v>3</v>
+      <c r="F34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>2</v>
@@ -5573,8 +5809,8 @@
       <c r="I34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>2</v>
+      <c r="J34" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K34" s="12" t="s">
         <v>9</v>
@@ -5588,11 +5824,11 @@
       <c r="N34" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="O34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>2</v>
+      <c r="O34" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="P34" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="Q34" s="1" t="s">
         <v>2</v>
@@ -5600,20 +5836,20 @@
       <c r="R34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="S34" s="1" t="s">
-        <v>2</v>
+      <c r="S34" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="T34" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V34" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="W34" s="4" t="s">
-        <v>8</v>
+        <v>23</v>
+      </c>
+      <c r="U34" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="V34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="X34" s="1" t="s">
         <v>2</v>
@@ -5630,35 +5866,35 @@
       <c r="AB34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AC34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI34" s="1" t="s">
-        <v>2</v>
+      <c r="AC34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF34" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG34" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH34" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI34" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AJ34" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL34" s="5" t="s">
-        <v>11</v>
+      <c r="AK34" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL34" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AM34" s="10" t="s">
         <v>12</v>
@@ -5666,8 +5902,8 @@
       <c r="AN34" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AO34" s="10" t="s">
-        <v>12</v>
+      <c r="AO34" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AP34" s="1" t="s">
         <v>2</v>
@@ -5697,12 +5933,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="35" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>2</v>
+      <c r="B35" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>3</v>
@@ -5713,20 +5949,20 @@
       <c r="E35" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F35" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>2</v>
+      <c r="F35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J35" s="12" t="s">
-        <v>9</v>
+      <c r="J35" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="K35" s="12" t="s">
         <v>9</v>
@@ -5743,26 +5979,26 @@
       <c r="O35" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="P35" s="1" t="s">
-        <v>2</v>
+      <c r="P35" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="Q35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="R35" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S35" s="4" t="s">
-        <v>27</v>
+      <c r="R35" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="S35" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="T35" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V35" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="U35" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>2</v>
@@ -5776,11 +6012,11 @@
       <c r="Z35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AA35" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB35" s="1" t="s">
-        <v>2</v>
+      <c r="AA35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB35" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AC35" s="5" t="s">
         <v>11</v>
@@ -5788,14 +6024,14 @@
       <c r="AD35" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AE35" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF35" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG35" s="1" t="s">
-        <v>2</v>
+      <c r="AE35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF35" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG35" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AH35" s="10" t="s">
         <v>12</v>
@@ -5803,8 +6039,8 @@
       <c r="AI35" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AJ35" s="5" t="s">
-        <v>11</v>
+      <c r="AJ35" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AK35" s="10" t="s">
         <v>12</v>
@@ -5812,20 +6048,20 @@
       <c r="AL35" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AM35" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AN35" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AO35" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP35" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ35" s="1" t="s">
-        <v>2</v>
+      <c r="AM35" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN35" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO35" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP35" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ35" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AR35" s="1" t="s">
         <v>2</v>
@@ -5836,11 +6072,11 @@
       <c r="AT35" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AU35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AV35" s="1" t="s">
-        <v>2</v>
+      <c r="AU35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AV35" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AW35" s="23" t="s">
         <v>2</v>
@@ -5849,7 +6085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="36" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>2</v>
       </c>
@@ -5862,11 +6098,11 @@
       <c r="D36" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E36" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>2</v>
+      <c r="E36" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>2</v>
@@ -5877,11 +6113,11 @@
       <c r="I36" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J36" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="K36" s="12" t="s">
-        <v>9</v>
+      <c r="J36" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="L36" s="12" t="s">
         <v>9</v>
@@ -5898,20 +6134,20 @@
       <c r="P36" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="Q36" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>2</v>
+      <c r="Q36" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="R36" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U36" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V36" s="1" t="s">
         <v>2</v>
@@ -5928,11 +6164,11 @@
       <c r="Z36" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AA36" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB36" s="1" t="s">
-        <v>2</v>
+      <c r="AA36" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB36" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AC36" s="5" t="s">
         <v>11</v>
@@ -5940,8 +6176,8 @@
       <c r="AD36" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AE36" s="5" t="s">
-        <v>11</v>
+      <c r="AE36" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AF36" s="10" t="s">
         <v>12</v>
@@ -5955,8 +6191,8 @@
       <c r="AI36" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AJ36" s="5" t="s">
-        <v>11</v>
+      <c r="AJ36" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AK36" s="10" t="s">
         <v>12</v>
@@ -5964,20 +6200,20 @@
       <c r="AL36" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AM36" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AN36" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AO36" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AP36" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AQ36" s="1" t="s">
-        <v>2</v>
+      <c r="AM36" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN36" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO36" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP36" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ36" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AR36" s="1" t="s">
         <v>2</v>
@@ -5988,22 +6224,22 @@
       <c r="AT36" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AU36" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AV36" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AW36" s="23" t="s">
-        <v>2</v>
+      <c r="AU36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AV36" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW36" s="27" t="s">
+        <v>9</v>
       </c>
       <c r="AX36" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A37" s="1" t="s">
-        <v>2</v>
+    <row r="37" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>3</v>
@@ -6011,20 +6247,20 @@
       <c r="C37" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D37" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>41</v>
+      <c r="D37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>2</v>
@@ -6032,8 +6268,8 @@
       <c r="J37" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K37" s="12" t="s">
-        <v>9</v>
+      <c r="K37" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="L37" s="12" t="s">
         <v>9</v>
@@ -6050,20 +6286,20 @@
       <c r="P37" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="Q37" s="1" t="s">
-        <v>2</v>
+      <c r="Q37" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="R37" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S37" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T37" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U37" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V37" s="1" t="s">
         <v>2</v>
@@ -6083,17 +6319,17 @@
       <c r="AA37" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AB37" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC37" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD37" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE37" s="5" t="s">
-        <v>11</v>
+      <c r="AB37" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC37" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD37" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE37" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AF37" s="10" t="s">
         <v>12</v>
@@ -6113,32 +6349,32 @@
       <c r="AK37" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AL37" s="10" t="s">
-        <v>12</v>
+      <c r="AL37" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="AM37" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AN37" s="11" t="s">
+      <c r="AN37" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AO37" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AO37" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AP37" s="10" t="s">
-        <v>12</v>
+      <c r="AP37" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="AQ37" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AR37" s="1" t="s">
-        <v>2</v>
+      <c r="AR37" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AS37" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AT37" s="5" t="s">
-        <v>11</v>
+      <c r="AT37" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="AU37" s="2" t="s">
         <v>6</v>
@@ -6146,31 +6382,31 @@
       <c r="AV37" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AW37" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="AX37" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A38" s="1" t="s">
-        <v>2</v>
+      <c r="AW37" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="AX37" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C38" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>3</v>
+      <c r="C38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F38" s="9" t="s">
-        <v>3</v>
+      <c r="F38" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>2</v>
@@ -6184,8 +6420,8 @@
       <c r="J38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>2</v>
+      <c r="K38" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="L38" s="12" t="s">
         <v>9</v>
@@ -6203,19 +6439,19 @@
         <v>9</v>
       </c>
       <c r="Q38" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="R38" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="R38" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="S38" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="S38" s="17" t="s">
-        <v>24</v>
-      </c>
       <c r="T38" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U38" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="V38" s="1" t="s">
         <v>2</v>
@@ -6232,17 +6468,17 @@
       <c r="Z38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AA38" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB38" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC38" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AD38" s="5" t="s">
-        <v>11</v>
+      <c r="AA38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB38" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC38" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD38" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AE38" s="10" t="s">
         <v>12</v>
@@ -6253,20 +6489,20 @@
       <c r="AG38" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AH38" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI38" s="10" t="s">
-        <v>12</v>
+      <c r="AH38" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI38" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="AJ38" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AK38" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL38" s="10" t="s">
-        <v>12</v>
+      <c r="AK38" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL38" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="AM38" s="11" t="s">
         <v>14</v>
@@ -6280,40 +6516,40 @@
       <c r="AP38" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AQ38" s="10" t="s">
-        <v>12</v>
+      <c r="AQ38" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AR38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AS38" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT38" s="5" t="s">
-        <v>11</v>
+      <c r="AS38" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AT38" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="AU38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AV38" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AW38" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="AX38" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A39" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>3</v>
+      <c r="AV38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AW38" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="AX38" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>2</v>
@@ -6321,11 +6557,11 @@
       <c r="E39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>3</v>
+      <c r="F39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>2</v>
@@ -6336,8 +6572,8 @@
       <c r="J39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>2</v>
+      <c r="K39" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="L39" s="12" t="s">
         <v>9</v>
@@ -6348,29 +6584,29 @@
       <c r="N39" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="O39" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="P39" s="12" t="s">
-        <v>9</v>
+      <c r="O39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P39" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="Q39" s="12" t="s">
         <v>9</v>
       </c>
       <c r="R39" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S39" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T39" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="U39" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="V39" s="1" t="s">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="U39" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="V39" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="W39" s="1" t="s">
         <v>2</v>
@@ -6384,11 +6620,11 @@
       <c r="Z39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AA39" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AB39" s="10" t="s">
-        <v>12</v>
+      <c r="AA39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB39" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AC39" s="10" t="s">
         <v>12</v>
@@ -6396,73 +6632,73 @@
       <c r="AD39" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AE39" s="10" t="s">
-        <v>12</v>
+      <c r="AE39" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="AF39" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AG39" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AH39" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI39" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AJ39" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AK39" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL39" s="4" t="s">
-        <v>35</v>
+      <c r="AG39" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH39" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI39" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ39" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK39" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL39" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="AM39" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AN39" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO39" s="11" t="s">
+      <c r="AN39" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AP39" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AQ39" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AR39" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AS39" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT39" s="2" t="s">
-        <v>6</v>
+      <c r="AO39" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP39" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ39" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AR39" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AS39" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AT39" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AU39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AV39" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AW39" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="AX39" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A40" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>3</v>
+      <c r="AV39" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AW39" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="AX39" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>2</v>
@@ -6488,8 +6724,8 @@
       <c r="J40" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K40" s="12" t="s">
-        <v>9</v>
+      <c r="K40" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="L40" s="12" t="s">
         <v>9</v>
@@ -6497,35 +6733,35 @@
       <c r="M40" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="N40" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="O40" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="P40" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q40" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="R40" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="S40" s="14" t="s">
-        <v>33</v>
+      <c r="N40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P40" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q40" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="R40" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="S40" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="T40" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U40" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="V40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W40" s="1" t="s">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="V40" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="W40" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="X40" s="1" t="s">
         <v>2</v>
@@ -6554,8 +6790,8 @@
       <c r="AF40" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AG40" s="10" t="s">
-        <v>12</v>
+      <c r="AG40" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="AH40" s="11" t="s">
         <v>14</v>
@@ -6563,8 +6799,8 @@
       <c r="AI40" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AJ40" s="10" t="s">
-        <v>12</v>
+      <c r="AJ40" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="AK40" s="11" t="s">
         <v>14</v>
@@ -6575,8 +6811,8 @@
       <c r="AM40" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AN40" s="11" t="s">
-        <v>14</v>
+      <c r="AN40" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AO40" s="10" t="s">
         <v>12</v>
@@ -6584,23 +6820,23 @@
       <c r="AP40" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AQ40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR40" s="1" t="s">
-        <v>2</v>
+      <c r="AQ40" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AR40" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AS40" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AT40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AU40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AV40" s="2" t="s">
-        <v>6</v>
+      <c r="AT40" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU40" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AV40" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AW40" s="28" t="s">
         <v>3</v>
@@ -6609,7 +6845,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="41" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>2</v>
       </c>
@@ -6640,44 +6876,44 @@
       <c r="J41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K41" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="L41" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="M41" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="N41" s="12" t="s">
-        <v>9</v>
+      <c r="K41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="O41" s="1" t="s">
         <v>2</v>
       </c>
       <c r="P41" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q41" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="R41" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="S41" s="17" t="s">
-        <v>24</v>
+      <c r="R41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S41" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="U41" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="V41" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="W41" s="1" t="s">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="U41" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="V41" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="W41" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="X41" s="1" t="s">
         <v>2</v>
@@ -6694,17 +6930,17 @@
       <c r="AB41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AC41" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD41" s="10" t="s">
-        <v>12</v>
+      <c r="AC41" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD41" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="AE41" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AF41" s="10" t="s">
-        <v>12</v>
+      <c r="AF41" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="AG41" s="11" t="s">
         <v>14</v>
@@ -6727,8 +6963,8 @@
       <c r="AM41" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AN41" s="11" t="s">
-        <v>14</v>
+      <c r="AN41" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AO41" s="10" t="s">
         <v>12</v>
@@ -6742,14 +6978,14 @@
       <c r="AR41" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AS41" s="5" t="s">
-        <v>11</v>
+      <c r="AS41" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AT41" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AU41" s="2" t="s">
-        <v>6</v>
+      <c r="AU41" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AV41" s="9" t="s">
         <v>3</v>
@@ -6761,7 +6997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="42" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>2</v>
       </c>
@@ -6789,17 +7025,17 @@
       <c r="I42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L42" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="M42" s="12" t="s">
-        <v>9</v>
+      <c r="J42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>2</v>
@@ -6808,31 +7044,31 @@
         <v>2</v>
       </c>
       <c r="P42" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q42" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="R42" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="S42" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="T42" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="U42" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="V42" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W42" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="X42" s="1" t="s">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="X42" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="Y42" s="6" t="s">
         <v>5</v>
@@ -6843,14 +7079,14 @@
       <c r="AA42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AB42" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC42" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD42" s="10" t="s">
-        <v>12</v>
+      <c r="AB42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD42" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="AE42" s="10" t="s">
         <v>12</v>
@@ -6867,8 +7103,8 @@
       <c r="AI42" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AJ42" s="11" t="s">
-        <v>14</v>
+      <c r="AJ42" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AK42" s="11" t="s">
         <v>14</v>
@@ -6879,14 +7115,14 @@
       <c r="AM42" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="AN42" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AO42" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AP42" s="10" t="s">
-        <v>12</v>
+      <c r="AN42" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO42" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AP42" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AQ42" s="10" t="s">
         <v>12</v>
@@ -6894,8 +7130,8 @@
       <c r="AR42" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AS42" s="5" t="s">
-        <v>11</v>
+      <c r="AS42" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AT42" s="5" t="s">
         <v>11</v>
@@ -6903,17 +7139,17 @@
       <c r="AU42" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AV42" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AW42" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX42" s="9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+      <c r="AV42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW42" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX42" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>2</v>
       </c>
@@ -6938,17 +7174,17 @@
       <c r="H43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I43" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>2</v>
+      <c r="I43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>2</v>
+      <c r="L43" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>2</v>
@@ -6956,14 +7192,14 @@
       <c r="N43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O43" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P43" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q43" s="12" t="s">
-        <v>9</v>
+      <c r="O43" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="R43" s="1" t="s">
         <v>2</v>
@@ -6971,20 +7207,20 @@
       <c r="S43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="T43" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="U43" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="V43" s="17" t="s">
-        <v>24</v>
+      <c r="T43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="W43" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="X43" s="1" t="s">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="X43" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="Y43" s="6" t="s">
         <v>5</v>
@@ -6995,41 +7231,41 @@
       <c r="AA43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AB43" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC43" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD43" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE43" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF43" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG43" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH43" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI43" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ43" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK43" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL43" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM43" s="11" t="s">
-        <v>14</v>
+      <c r="AB43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD43" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM43" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AN43" s="10" t="s">
         <v>12</v>
@@ -7040,32 +7276,32 @@
       <c r="AP43" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AQ43" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AR43" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AS43" s="10" t="s">
-        <v>12</v>
+      <c r="AQ43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AR43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AS43" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AT43" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AU43" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AV43" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AW43" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX43" s="9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+      <c r="AU43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AV43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AW43" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="AX43" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>2</v>
       </c>
@@ -7087,11 +7323,11 @@
       <c r="G44" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H44" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>2</v>
+      <c r="H44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>18</v>
@@ -7108,14 +7344,14 @@
       <c r="N44" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O44" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P44" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>2</v>
+      <c r="O44" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="R44" s="1" t="s">
         <v>2</v>
@@ -7129,14 +7365,14 @@
       <c r="U44" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="V44" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="W44" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="X44" s="17" t="s">
-        <v>24</v>
+      <c r="V44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="X44" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="Y44" s="6" t="s">
         <v>5</v>
@@ -7150,53 +7386,53 @@
       <c r="AB44" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AC44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE44" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF44" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG44" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH44" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI44" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ44" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AK44" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL44" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM44" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AN44" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO44" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AP44" s="5" t="s">
-        <v>11</v>
+      <c r="AC44" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD44" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF44" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK44" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL44" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM44" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN44" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO44" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP44" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AQ44" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AR44" s="5" t="s">
-        <v>11</v>
+      <c r="AR44" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="AS44" s="1" t="s">
         <v>2</v>
@@ -7217,7 +7453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="45" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>2</v>
       </c>
@@ -7254,20 +7490,20 @@
       <c r="L45" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>2</v>
+      <c r="M45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="O45" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="Q45" s="1" t="s">
-        <v>2</v>
+      <c r="Q45" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>2</v>
@@ -7284,71 +7520,71 @@
       <c r="V45" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="W45" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="X45" s="17" t="s">
-        <v>24</v>
+      <c r="W45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="X45" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="Y45" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z45" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="AA45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC45" s="2" t="s">
-        <v>6</v>
+      <c r="AA45" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB45" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC45" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="AD45" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="AE45" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AF45" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG45" s="5" t="s">
-        <v>11</v>
+      <c r="AE45" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF45" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG45" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AH45" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AI45" s="10" t="s">
-        <v>12</v>
+      <c r="AI45" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AJ45" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK45" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL45" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AM45" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AN45" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AO45" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AP45" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AQ45" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AR45" s="10" t="s">
-        <v>12</v>
+      <c r="AK45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AN45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AO45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AP45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AQ45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AR45" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="AS45" s="1" t="s">
         <v>2</v>
@@ -7369,7 +7605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+    <row r="46" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>2</v>
       </c>
@@ -7391,29 +7627,29 @@
       <c r="G46" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>18</v>
+      <c r="H46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K46" s="3" t="s">
+      <c r="K46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M46" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L46" s="3" t="s">
+      <c r="N46" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="O46" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O46" s="17" t="s">
-        <v>24</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>18</v>
@@ -7442,17 +7678,17 @@
       <c r="X46" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Y46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB46" s="1" t="s">
-        <v>2</v>
+      <c r="Y46" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z46" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA46" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB46" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="AC46" s="18" t="s">
         <v>7</v>
@@ -7460,47 +7696,47 @@
       <c r="AD46" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="AE46" s="5" t="s">
-        <v>11</v>
+      <c r="AE46" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="AF46" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AG46" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AH46" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI46" s="5" t="s">
-        <v>11</v>
+      <c r="AG46" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH46" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI46" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AJ46" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK46" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL46" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AM46" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AN46" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AO46" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AP46" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AQ46" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="AR46" s="10" t="s">
-        <v>12</v>
+      <c r="AK46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AN46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AO46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AP46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AQ46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AR46" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AS46" s="1" t="s">
         <v>2</v>
@@ -7511,25 +7747,25 @@
       <c r="AU46" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AV46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AW46" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="AX46" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>2</v>
+      <c r="AV46" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AW46" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="AX46" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>2</v>
@@ -7546,32 +7782,32 @@
       <c r="H47" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O47" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>18</v>
+      <c r="I47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L47" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="R47" s="1" t="s">
         <v>2</v>
@@ -7597,8 +7833,8 @@
       <c r="Y47" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Z47" s="1" t="s">
-        <v>2</v>
+      <c r="Z47" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="AA47" s="18" t="s">
         <v>7</v>
@@ -7612,38 +7848,38 @@
       <c r="AD47" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="AE47" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF47" s="9" t="s">
-        <v>3</v>
+      <c r="AE47" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF47" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="AG47" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AH47" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI47" s="5" t="s">
-        <v>11</v>
+      <c r="AH47" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI47" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AJ47" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK47" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL47" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AM47" s="5" t="s">
-        <v>11</v>
+      <c r="AK47" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL47" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM47" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AN47" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AO47" s="5" t="s">
-        <v>11</v>
+      <c r="AO47" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AP47" s="5" t="s">
         <v>11</v>
@@ -7651,8 +7887,8 @@
       <c r="AQ47" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AR47" s="5" t="s">
-        <v>11</v>
+      <c r="AR47" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AS47" s="1" t="s">
         <v>2</v>
@@ -7663,17 +7899,17 @@
       <c r="AU47" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AV47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AW47" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="AX47" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
+      <c r="AV47" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AW47" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="AX47" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>2</v>
       </c>
@@ -7701,29 +7937,29 @@
       <c r="I48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N48" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>18</v>
+      <c r="J48" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="R48" s="1" t="s">
         <v>2</v>
@@ -7746,8 +7982,8 @@
       <c r="X48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Y48" s="18" t="s">
-        <v>7</v>
+      <c r="Y48" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="Z48" s="18" t="s">
         <v>7</v>
@@ -7767,8 +8003,8 @@
       <c r="AE48" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="AF48" s="9" t="s">
-        <v>3</v>
+      <c r="AF48" s="18" t="s">
+        <v>7</v>
       </c>
       <c r="AG48" s="9" t="s">
         <v>3</v>
@@ -7782,38 +8018,38 @@
       <c r="AJ48" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AK48" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL48" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AM48" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AN48" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AO48" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AP48" s="5" t="s">
-        <v>11</v>
+      <c r="AK48" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL48" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM48" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN48" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO48" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP48" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AQ48" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="AR48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT48" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AU48" s="5" t="s">
-        <v>11</v>
+      <c r="AR48" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS48" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT48" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU48" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AV48" s="9" t="s">
         <v>3</v>
@@ -7821,19 +8057,19 @@
       <c r="AW48" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="AX48" s="9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A49" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>24</v>
+      <c r="AX48" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>2</v>
@@ -7853,17 +8089,17 @@
       <c r="I49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>2</v>
+      <c r="J49" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L49" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="M49" s="17" t="s">
-        <v>24</v>
+      <c r="L49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="N49" s="1" t="s">
         <v>2</v>
@@ -7913,14 +8149,14 @@
       <c r="AC49" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="AD49" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE49" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF49" s="18" t="s">
-        <v>7</v>
+      <c r="AD49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF49" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="AG49" s="9" t="s">
         <v>3</v>
@@ -7931,64 +8167,64 @@
       <c r="AI49" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="AJ49" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK49" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AL49" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM49" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AN49" s="5" t="s">
-        <v>11</v>
+      <c r="AJ49" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK49" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL49" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM49" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN49" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AO49" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AP49" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AQ49" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AR49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT49" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AU49" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AV49" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AW49" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX49" s="9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>2</v>
+      <c r="AP49" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ49" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AR49" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS49" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT49" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU49" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV49" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW49" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="AX49" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="17" t="s">
+        <v>23</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>2</v>
@@ -8002,17 +8238,17 @@
       <c r="H50" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K50" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="L50" s="4" t="s">
-        <v>8</v>
+      <c r="I50" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>2</v>
@@ -8053,50 +8289,50 @@
       <c r="Y50" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Z50" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA50" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB50" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC50" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD50" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE50" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF50" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG50" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH50" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI50" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ50" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK50" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AL50" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM50" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AN50" s="12" t="s">
-        <v>9</v>
+      <c r="Z50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AH50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ50" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK50" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL50" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM50" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN50" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="AO50" s="12" t="s">
         <v>9</v>
@@ -8104,8 +8340,8 @@
       <c r="AP50" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AQ50" s="5" t="s">
-        <v>11</v>
+      <c r="AQ50" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="AR50" s="12" t="s">
         <v>9</v>
@@ -8119,612 +8355,309 @@
       <c r="AU50" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AV50" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AW50" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="AX50" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="51" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A51" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="J51" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z51" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA51" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB51" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC51" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG51" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AH51" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI51" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AJ51" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK51" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AL51" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AM51" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AN51" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO51" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AP51" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AQ51" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AR51" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS51" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AT51" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AU51" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AV51" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AW51" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="AX51" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:50" ht="50" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A52" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I52" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="O52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="P52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="S52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="V52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="W52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="X52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="Z52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AB52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AC52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AD52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AH52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AI52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ52" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AK52" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="AL52" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AM52" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AN52" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO52" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AP52" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AQ52" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AR52" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS52" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AT52" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AU52" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AV52" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="AW52" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="AX52" s="12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:50" ht="45" thickTop="1">
-      <c r="A53" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="31"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
-      <c r="O53" s="31"/>
-      <c r="P53" s="31"/>
-      <c r="Q53" s="31"/>
-      <c r="R53" s="31"/>
-      <c r="S53" s="31"/>
-      <c r="T53" s="31"/>
-      <c r="U53" s="31"/>
-      <c r="V53" s="31"/>
-      <c r="W53" s="31"/>
-      <c r="X53" s="31"/>
-      <c r="Y53" s="31"/>
-      <c r="Z53" s="31"/>
-      <c r="AA53" s="31"/>
-      <c r="AB53" s="31"/>
-      <c r="AC53" s="31"/>
-      <c r="AD53" s="31"/>
-      <c r="AE53" s="31"/>
-      <c r="AF53" s="31"/>
-      <c r="AG53" s="31"/>
-      <c r="AH53" s="31"/>
-      <c r="AI53" s="31"/>
-      <c r="AJ53" s="31"/>
-      <c r="AK53" s="31"/>
-      <c r="AL53" s="31"/>
-      <c r="AM53" s="31"/>
-      <c r="AN53" s="31"/>
-      <c r="AO53" s="31"/>
-      <c r="AP53" s="31"/>
-      <c r="AQ53" s="31"/>
-      <c r="AR53" s="31"/>
-      <c r="AS53" s="31"/>
-      <c r="AT53" s="31"/>
-      <c r="AU53" s="31"/>
-      <c r="AV53" s="31"/>
-      <c r="AW53" s="31"/>
-      <c r="AX53" s="31"/>
-    </row>
-    <row r="54" spans="1:50" ht="13">
+      <c r="AV50" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW50" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="AX50" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:50" ht="45" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
+      <c r="P51" s="30"/>
+      <c r="Q51" s="30"/>
+      <c r="R51" s="30"/>
+      <c r="S51" s="30"/>
+      <c r="T51" s="30"/>
+      <c r="U51" s="30"/>
+      <c r="V51" s="30"/>
+      <c r="W51" s="30"/>
+      <c r="X51" s="30"/>
+      <c r="Y51" s="30"/>
+      <c r="Z51" s="30"/>
+      <c r="AA51" s="30"/>
+      <c r="AB51" s="30"/>
+      <c r="AC51" s="30"/>
+      <c r="AD51" s="30"/>
+      <c r="AE51" s="30"/>
+      <c r="AF51" s="30"/>
+      <c r="AG51" s="30"/>
+      <c r="AH51" s="30"/>
+      <c r="AI51" s="30"/>
+      <c r="AJ51" s="30"/>
+      <c r="AK51" s="30"/>
+      <c r="AL51" s="30"/>
+      <c r="AM51" s="30"/>
+      <c r="AN51" s="30"/>
+      <c r="AO51" s="30"/>
+      <c r="AP51" s="30"/>
+      <c r="AQ51" s="30"/>
+      <c r="AR51" s="30"/>
+      <c r="AS51" s="30"/>
+      <c r="AT51" s="30"/>
+      <c r="AU51" s="30"/>
+      <c r="AV51" s="30"/>
+      <c r="AW51" s="30"/>
+      <c r="AX51" s="30"/>
+    </row>
+    <row r="52" spans="1:50" ht="13" x14ac:dyDescent="0.15">
+      <c r="AX52" s="21"/>
+    </row>
+    <row r="53" spans="1:50" ht="13" x14ac:dyDescent="0.15">
+      <c r="AX53" s="21"/>
+    </row>
+    <row r="54" spans="1:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX54" s="21"/>
     </row>
-    <row r="55" spans="1:50" ht="13">
+    <row r="55" spans="1:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX55" s="21"/>
     </row>
-    <row r="56" spans="1:50" ht="13">
+    <row r="56" spans="1:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX56" s="21"/>
     </row>
-    <row r="57" spans="1:50" ht="13">
+    <row r="57" spans="1:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX57" s="21"/>
     </row>
-    <row r="58" spans="1:50" ht="13">
+    <row r="58" spans="1:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX58" s="21"/>
     </row>
-    <row r="59" spans="1:50" ht="13">
+    <row r="59" spans="1:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX59" s="21"/>
     </row>
-    <row r="60" spans="1:50" ht="13">
+    <row r="60" spans="1:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX60" s="21"/>
     </row>
-    <row r="61" spans="1:50" ht="13">
+    <row r="61" spans="1:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX61" s="21"/>
     </row>
-    <row r="62" spans="1:50" ht="13">
+    <row r="62" spans="1:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX62" s="21"/>
     </row>
-    <row r="63" spans="1:50" ht="13">
+    <row r="63" spans="1:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX63" s="21"/>
     </row>
-    <row r="64" spans="1:50" ht="13">
+    <row r="64" spans="1:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX64" s="21"/>
     </row>
-    <row r="65" spans="50:50" ht="13">
+    <row r="65" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX65" s="21"/>
     </row>
-    <row r="66" spans="50:50" ht="13">
+    <row r="66" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX66" s="21"/>
     </row>
-    <row r="67" spans="50:50" ht="13">
+    <row r="67" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX67" s="21"/>
     </row>
-    <row r="68" spans="50:50" ht="13">
+    <row r="68" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX68" s="21"/>
     </row>
-    <row r="69" spans="50:50" ht="13">
+    <row r="69" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX69" s="21"/>
     </row>
-    <row r="70" spans="50:50" ht="13">
+    <row r="70" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX70" s="21"/>
     </row>
-    <row r="71" spans="50:50" ht="13">
+    <row r="71" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX71" s="21"/>
     </row>
-    <row r="72" spans="50:50" ht="13">
+    <row r="72" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX72" s="21"/>
     </row>
-    <row r="73" spans="50:50" ht="13">
+    <row r="73" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX73" s="21"/>
     </row>
-    <row r="74" spans="50:50" ht="13">
+    <row r="74" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX74" s="21"/>
     </row>
-    <row r="75" spans="50:50" ht="13">
+    <row r="75" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX75" s="21"/>
     </row>
-    <row r="76" spans="50:50" ht="13">
+    <row r="76" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX76" s="21"/>
     </row>
-    <row r="77" spans="50:50" ht="13">
+    <row r="77" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX77" s="21"/>
     </row>
-    <row r="78" spans="50:50" ht="13">
+    <row r="78" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX78" s="21"/>
     </row>
-    <row r="79" spans="50:50" ht="13">
+    <row r="79" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX79" s="21"/>
     </row>
-    <row r="80" spans="50:50" ht="13">
+    <row r="80" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX80" s="21"/>
     </row>
-    <row r="81" spans="50:50" ht="13">
+    <row r="81" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX81" s="21"/>
     </row>
-    <row r="82" spans="50:50" ht="13">
+    <row r="82" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX82" s="21"/>
     </row>
-    <row r="83" spans="50:50" ht="13">
+    <row r="83" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX83" s="21"/>
     </row>
-    <row r="84" spans="50:50" ht="13">
+    <row r="84" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX84" s="21"/>
     </row>
-    <row r="85" spans="50:50" ht="13">
+    <row r="85" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX85" s="21"/>
     </row>
-    <row r="86" spans="50:50" ht="13">
+    <row r="86" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX86" s="21"/>
     </row>
-    <row r="87" spans="50:50" ht="13">
+    <row r="87" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX87" s="21"/>
     </row>
-    <row r="88" spans="50:50" ht="13">
+    <row r="88" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX88" s="21"/>
     </row>
-    <row r="89" spans="50:50" ht="13">
+    <row r="89" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX89" s="21"/>
     </row>
-    <row r="90" spans="50:50" ht="13">
+    <row r="90" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX90" s="21"/>
     </row>
-    <row r="91" spans="50:50" ht="13">
+    <row r="91" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX91" s="21"/>
     </row>
-    <row r="92" spans="50:50" ht="13">
+    <row r="92" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX92" s="21"/>
     </row>
-    <row r="93" spans="50:50" ht="13">
+    <row r="93" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX93" s="21"/>
     </row>
-    <row r="94" spans="50:50" ht="13">
+    <row r="94" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX94" s="21"/>
     </row>
-    <row r="95" spans="50:50" ht="13">
+    <row r="95" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX95" s="21"/>
     </row>
-    <row r="96" spans="50:50" ht="13">
+    <row r="96" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX96" s="21"/>
     </row>
-    <row r="97" spans="50:50" ht="13">
+    <row r="97" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX97" s="21"/>
     </row>
-    <row r="98" spans="50:50" ht="13">
+    <row r="98" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX98" s="21"/>
     </row>
-    <row r="99" spans="50:50" ht="13">
+    <row r="99" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX99" s="21"/>
     </row>
-    <row r="100" spans="50:50" ht="13">
+    <row r="100" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX100" s="21"/>
     </row>
-    <row r="101" spans="50:50" ht="13">
+    <row r="101" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX101" s="21"/>
     </row>
-    <row r="102" spans="50:50" ht="13">
+    <row r="102" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX102" s="21"/>
     </row>
-    <row r="103" spans="50:50" ht="13">
+    <row r="103" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX103" s="21"/>
     </row>
-    <row r="104" spans="50:50" ht="13">
+    <row r="104" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX104" s="21"/>
     </row>
-    <row r="105" spans="50:50" ht="13">
+    <row r="105" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX105" s="21"/>
     </row>
-    <row r="106" spans="50:50" ht="13">
+    <row r="106" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX106" s="21"/>
     </row>
-    <row r="107" spans="50:50" ht="13">
+    <row r="107" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX107" s="21"/>
     </row>
-    <row r="108" spans="50:50" ht="13">
+    <row r="108" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX108" s="21"/>
     </row>
-    <row r="109" spans="50:50" ht="13">
+    <row r="109" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX109" s="21"/>
     </row>
-    <row r="110" spans="50:50" ht="13">
+    <row r="110" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX110" s="21"/>
     </row>
-    <row r="111" spans="50:50" ht="13">
+    <row r="111" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX111" s="21"/>
     </row>
-    <row r="112" spans="50:50" ht="13">
+    <row r="112" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX112" s="21"/>
     </row>
-    <row r="113" spans="50:50" ht="13">
+    <row r="113" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX113" s="21"/>
     </row>
-    <row r="114" spans="50:50" ht="13">
+    <row r="114" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX114" s="21"/>
     </row>
-    <row r="115" spans="50:50" ht="13">
+    <row r="115" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX115" s="21"/>
     </row>
-    <row r="116" spans="50:50" ht="13">
+    <row r="116" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX116" s="21"/>
     </row>
-    <row r="117" spans="50:50" ht="13">
+    <row r="117" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX117" s="21"/>
     </row>
-    <row r="118" spans="50:50" ht="13">
+    <row r="118" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX118" s="21"/>
     </row>
-    <row r="119" spans="50:50" ht="13">
+    <row r="119" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX119" s="21"/>
     </row>
-    <row r="120" spans="50:50" ht="13">
+    <row r="120" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX120" s="21"/>
     </row>
-    <row r="121" spans="50:50" ht="13">
+    <row r="121" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX121" s="21"/>
     </row>
-    <row r="122" spans="50:50" ht="13">
+    <row r="122" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX122" s="21"/>
     </row>
-    <row r="123" spans="50:50" ht="13">
+    <row r="123" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX123" s="21"/>
     </row>
-    <row r="124" spans="50:50" ht="13">
+    <row r="124" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX124" s="21"/>
     </row>
-    <row r="125" spans="50:50" ht="13">
+    <row r="125" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX125" s="21"/>
     </row>
-    <row r="126" spans="50:50" ht="13">
+    <row r="126" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX126" s="21"/>
     </row>
-    <row r="127" spans="50:50" ht="13">
+    <row r="127" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX127" s="21"/>
     </row>
-    <row r="128" spans="50:50" ht="13">
+    <row r="128" spans="50:50" ht="13" x14ac:dyDescent="0.15">
       <c r="AX128" s="21"/>
     </row>
-    <row r="129" spans="50:50" ht="13">
+    <row r="129" spans="50:50" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="AX129" s="21"/>
     </row>
-    <row r="130" spans="50:50" ht="13">
-      <c r="AX130" s="21"/>
-    </row>
-    <row r="131" spans="50:50" ht="14" thickBot="1">
-      <c r="AX131" s="21"/>
-    </row>
+    <row r="130" spans="50:50" ht="13" x14ac:dyDescent="0.15"/>
+    <row r="131" spans="50:50" ht="13" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:AX2"/>
-    <mergeCell ref="A53:AX53"/>
+  <mergeCells count="1">
+    <mergeCell ref="A51:AX51"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
